--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98358</v>
+        <v>98365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1760,54 +1760,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>78634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865114</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,13 +1892,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460227</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840330</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,48 +2254,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>79556</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R18" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,57 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>79556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R19" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1760,45 +1760,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B13" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1868,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,13 +1901,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,54 +1963,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>78634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125865020</v>
       </c>
       <c r="B16" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460224</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840345</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125865416</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125866011</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125864782</v>
       </c>
       <c r="B5" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125864869</v>
       </c>
       <c r="B6" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125864847</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B9" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R9" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>125864716</v>
       </c>
       <c r="B12" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,57 +1760,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B13" t="n">
-        <v>98331</v>
+        <v>79586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R13" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R14" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78634</v>
+        <v>98332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>125865994</v>
       </c>
       <c r="B17" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R9" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R10" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865020</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>78635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460224</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840345</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865199</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>78635</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460248</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840343</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125865416</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125866011</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125864782</v>
       </c>
       <c r="B5" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125864869</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125864847</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B9" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R9" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125864850</v>
+        <v>125866168</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460167</v>
+        <v>460391</v>
       </c>
       <c r="R11" t="n">
-        <v>6840353</v>
+        <v>6840167</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>125864716</v>
       </c>
       <c r="B12" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125865114</v>
       </c>
       <c r="B13" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460227</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,48 +1857,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,54 +1963,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>78639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125865020</v>
       </c>
       <c r="B16" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460224</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840345</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>125865994</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R10" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R11" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,57 +1857,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1954,54 +1954,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865114</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460227</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840330</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,45 +2051,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125866547</v>
       </c>
       <c r="B16" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460380</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840200</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125865416</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125866011</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125864782</v>
       </c>
       <c r="B5" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125864869</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125864847</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125864850</v>
+        <v>125865368</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460167</v>
+        <v>460304</v>
       </c>
       <c r="R9" t="n">
-        <v>6840353</v>
+        <v>6840312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R11" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>125864716</v>
       </c>
       <c r="B12" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865114</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460227</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840330</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,54 +2060,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125866547</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460380</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840200</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>125865994</v>
       </c>
       <c r="B17" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2254,57 +2254,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>79562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R18" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2360,48 +2351,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R19" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125864850</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460167</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840353</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125864850</v>
+        <v>125866168</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460167</v>
+        <v>460391</v>
       </c>
       <c r="R11" t="n">
-        <v>6840353</v>
+        <v>6840167</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125865114</v>
       </c>
       <c r="B13" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460227</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,48 +1857,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,54 +1963,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>78640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125865020</v>
       </c>
       <c r="B16" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460224</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840345</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125864850</v>
+        <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460167</v>
+        <v>460391</v>
       </c>
       <c r="R10" t="n">
-        <v>6840353</v>
+        <v>6840167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125866168</v>
+        <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460391</v>
+        <v>460167</v>
       </c>
       <c r="R11" t="n">
-        <v>6840167</v>
+        <v>6840353</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,57 +1857,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78640</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,48 +2254,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>79562</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R18" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,57 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>79562</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R19" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125865020</v>
       </c>
       <c r="B13" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460224</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840345</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,48 +1857,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,54 +1963,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>78640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865020</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460224</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840345</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,57 +1857,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,45 +1954,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>78640</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B9" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R9" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125864850</v>
+        <v>125866168</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460167</v>
+        <v>460391</v>
       </c>
       <c r="R11" t="n">
-        <v>6840353</v>
+        <v>6840167</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125865114</v>
       </c>
       <c r="B13" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460227</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,48 +1857,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,57 +1963,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B16" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125865416</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125866011</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125864782</v>
       </c>
       <c r="B5" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125864869</v>
       </c>
       <c r="B6" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125864847</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125864850</v>
+        <v>125865368</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460167</v>
+        <v>460304</v>
       </c>
       <c r="R9" t="n">
-        <v>6840353</v>
+        <v>6840312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R10" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125866168</v>
+        <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460391</v>
+        <v>460167</v>
       </c>
       <c r="R11" t="n">
-        <v>6840167</v>
+        <v>6840353</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>125864716</v>
       </c>
       <c r="B12" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R13" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,57 +1857,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>79595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1963,48 +1954,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865199</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460248</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840343</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>125865994</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2254,57 +2254,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>79566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R18" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2360,48 +2351,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B19" t="n">
-        <v>79562</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R19" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -2254,48 +2254,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>79566</v>
+        <v>98349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R18" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,57 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>98349</v>
+        <v>79566</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R19" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B9" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R9" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1760,45 +1760,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865199</v>
+        <v>125866547</v>
       </c>
       <c r="B13" t="n">
-        <v>78644</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460248</v>
+        <v>460380</v>
       </c>
       <c r="R13" t="n">
-        <v>6840343</v>
+        <v>6840200</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B14" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1868,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,13 +1901,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,57 +1963,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B16" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B10" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R10" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125864850</v>
+        <v>125865368</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460167</v>
+        <v>460304</v>
       </c>
       <c r="R11" t="n">
-        <v>6840353</v>
+        <v>6840312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,57 +1760,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125866547</v>
+        <v>125865020</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460380</v>
+        <v>460224</v>
       </c>
       <c r="R13" t="n">
-        <v>6840200</v>
+        <v>6840345</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865114</v>
+        <v>125865199</v>
       </c>
       <c r="B14" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460227</v>
+        <v>460248</v>
       </c>
       <c r="R14" t="n">
-        <v>6840330</v>
+        <v>6840343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,48 +1954,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125865020</v>
+        <v>125866547</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460224</v>
+        <v>460380</v>
       </c>
       <c r="R15" t="n">
-        <v>6840345</v>
+        <v>6840200</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865199</v>
+        <v>125865114</v>
       </c>
       <c r="B16" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460248</v>
+        <v>460227</v>
       </c>
       <c r="R16" t="n">
-        <v>6840343</v>
+        <v>6840330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R9" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125864850</v>
+        <v>125866168</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460167</v>
+        <v>460391</v>
       </c>
       <c r="R10" t="n">
-        <v>6840353</v>
+        <v>6840167</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R11" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -2254,57 +2254,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>79566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R18" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2360,48 +2351,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B19" t="n">
-        <v>79566</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R19" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125865416</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125866011</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125865752</v>
       </c>
       <c r="B4" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>125864782</v>
       </c>
       <c r="B5" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>125864869</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125864847</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125866245</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125865368</v>
+        <v>125866168</v>
       </c>
       <c r="B9" t="n">
-        <v>78644</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460304</v>
+        <v>460391</v>
       </c>
       <c r="R9" t="n">
-        <v>6840312</v>
+        <v>6840167</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125866168</v>
+        <v>125865368</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460391</v>
+        <v>460304</v>
       </c>
       <c r="R10" t="n">
-        <v>6840167</v>
+        <v>6840312</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>125864850</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>125864716</v>
       </c>
       <c r="B12" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R13" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865199</v>
+        <v>125865020</v>
       </c>
       <c r="B14" t="n">
-        <v>78644</v>
+        <v>79598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460248</v>
+        <v>460224</v>
       </c>
       <c r="R14" t="n">
-        <v>6840343</v>
+        <v>6840345</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1954,54 +1954,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125866547</v>
+        <v>125865199</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460380</v>
+        <v>460248</v>
       </c>
       <c r="R15" t="n">
-        <v>6840200</v>
+        <v>6840343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,45 +2051,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125865114</v>
+        <v>125866547</v>
       </c>
       <c r="B16" t="n">
-        <v>78736</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460227</v>
+        <v>460380</v>
       </c>
       <c r="R16" t="n">
-        <v>6840330</v>
+        <v>6840200</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>125865994</v>
       </c>
       <c r="B17" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2254,48 +2254,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125865401</v>
+        <v>125866606</v>
       </c>
       <c r="B18" t="n">
-        <v>79566</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460309</v>
+        <v>460384</v>
       </c>
       <c r="R18" t="n">
-        <v>6840300</v>
+        <v>6840195</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,57 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125866606</v>
+        <v>125865401</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>79569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarberget, Hammarberget, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460384</v>
+        <v>460309</v>
       </c>
       <c r="R19" t="n">
-        <v>6840195</v>
+        <v>6840300</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125865114</v>
+        <v>125865020</v>
       </c>
       <c r="B13" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460227</v>
+        <v>460224</v>
       </c>
       <c r="R13" t="n">
-        <v>6840330</v>
+        <v>6840345</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125865020</v>
+        <v>125865114</v>
       </c>
       <c r="B14" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460224</v>
+        <v>460227</v>
       </c>
       <c r="R14" t="n">
-        <v>6840345</v>
+        <v>6840330</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 2737-2025 artfynd.xlsx
+++ b/artfynd/A 2737-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125865368</v>
+        <v>125864850</v>
       </c>
       <c r="B10" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460304</v>
+        <v>460167</v>
       </c>
       <c r="R10" t="n">
-        <v>6840312</v>
+        <v>6840353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125864850</v>
+        <v>125865368</v>
       </c>
       <c r="B11" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460167</v>
+        <v>460304</v>
       </c>
       <c r="R11" t="n">
-        <v>6840353</v>
+        <v>6840312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
